--- a/others/BURNDOWN-CHART.xlsx
+++ b/others/BURNDOWN-CHART.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/enric/Documents/UNI Informatica/3r - Q2/E.Software/Projecte/others/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8A507A65-DCC9-CE41-B208-44DF48FF1E83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFD7C60C-220D-6845-8389-0907E3B299F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -95,7 +95,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -134,6 +134,12 @@
     </font>
     <font>
       <sz val="14"/>
+      <color theme="1"/>
+      <name val="Century Gothic"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Century Gothic"/>
       <family val="1"/>
@@ -460,7 +466,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -534,10 +540,13 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -618,37 +627,37 @@
                   <c:v>29</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>29</c:v>
+                  <c:v>27</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>29</c:v>
+                  <c:v>24</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>29</c:v>
+                  <c:v>24</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>29</c:v>
+                  <c:v>24</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>29</c:v>
+                  <c:v>24</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>29</c:v>
+                  <c:v>24</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>29</c:v>
+                  <c:v>24</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>29</c:v>
+                  <c:v>24</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>29</c:v>
+                  <c:v>24</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>29</c:v>
+                  <c:v>24</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>29</c:v>
+                  <c:v>24</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -700,37 +709,37 @@
                   <c:v>30</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>30</c:v>
+                  <c:v>28</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>30</c:v>
+                  <c:v>25.5</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>30</c:v>
+                  <c:v>25.5</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>30</c:v>
+                  <c:v>25.5</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>30</c:v>
+                  <c:v>25.5</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>30</c:v>
+                  <c:v>25.5</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>30</c:v>
+                  <c:v>25.5</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>30</c:v>
+                  <c:v>25.5</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>30</c:v>
+                  <c:v>25.5</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>30</c:v>
+                  <c:v>25.5</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>30</c:v>
+                  <c:v>25.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1227,13 +1236,13 @@
     </row>
     <row r="3" spans="1:26" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3"/>
-      <c r="B3" s="29" t="s">
+      <c r="B3" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="27"/>
-      <c r="D3" s="27"/>
-      <c r="E3" s="27"/>
-      <c r="F3" s="28"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="29"/>
       <c r="G3" s="7"/>
       <c r="H3" s="8">
         <v>46096</v>
@@ -1532,15 +1541,19 @@
       <c r="B11" s="16">
         <v>5</v>
       </c>
-      <c r="C11" s="17"/>
-      <c r="D11" s="18"/>
+      <c r="C11" s="17">
+        <v>2</v>
+      </c>
+      <c r="D11" s="18">
+        <v>2</v>
+      </c>
       <c r="E11" s="21">
         <f t="shared" ref="E11:F11" si="4">E10-C11</f>
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F11" s="22">
         <f t="shared" si="4"/>
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
@@ -1568,15 +1581,19 @@
       <c r="B12" s="16">
         <v>6</v>
       </c>
-      <c r="C12" s="17"/>
-      <c r="D12" s="18"/>
+      <c r="C12" s="17">
+        <v>3</v>
+      </c>
+      <c r="D12" s="30">
+        <v>2.5</v>
+      </c>
       <c r="E12" s="21">
         <f t="shared" ref="E12:F12" si="5">E11-C12</f>
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F12" s="22">
         <f t="shared" si="5"/>
-        <v>30</v>
+        <v>25.5</v>
       </c>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
@@ -1608,11 +1625,11 @@
       <c r="D13" s="18"/>
       <c r="E13" s="21">
         <f t="shared" ref="E13:F13" si="6">E12-C13</f>
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F13" s="22">
         <f t="shared" si="6"/>
-        <v>30</v>
+        <v>25.5</v>
       </c>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
@@ -1644,11 +1661,11 @@
       <c r="D14" s="18"/>
       <c r="E14" s="21">
         <f t="shared" ref="E14:F14" si="7">E13-C14</f>
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F14" s="22">
         <f t="shared" si="7"/>
-        <v>30</v>
+        <v>25.5</v>
       </c>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
@@ -1680,11 +1697,11 @@
       <c r="D15" s="18"/>
       <c r="E15" s="21">
         <f t="shared" ref="E15:F15" si="8">E14-C15</f>
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F15" s="22">
         <f t="shared" si="8"/>
-        <v>30</v>
+        <v>25.5</v>
       </c>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
@@ -1716,11 +1733,11 @@
       <c r="D16" s="18"/>
       <c r="E16" s="21">
         <f t="shared" ref="E16:F16" si="9">E15-C16</f>
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F16" s="22">
         <f t="shared" si="9"/>
-        <v>30</v>
+        <v>25.5</v>
       </c>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
@@ -1752,11 +1769,11 @@
       <c r="D17" s="18"/>
       <c r="E17" s="21">
         <f t="shared" ref="E17:F17" si="10">E16-C17</f>
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F17" s="22">
         <f t="shared" si="10"/>
-        <v>30</v>
+        <v>25.5</v>
       </c>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
@@ -1788,11 +1805,11 @@
       <c r="D18" s="18"/>
       <c r="E18" s="21">
         <f t="shared" ref="E18:F18" si="11">E17-C18</f>
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F18" s="22">
         <f t="shared" si="11"/>
-        <v>30</v>
+        <v>25.5</v>
       </c>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
@@ -1824,11 +1841,11 @@
       <c r="D19" s="18"/>
       <c r="E19" s="21">
         <f t="shared" ref="E19:F19" si="12">E18-C19</f>
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F19" s="22">
         <f t="shared" si="12"/>
-        <v>30</v>
+        <v>25.5</v>
       </c>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
@@ -1860,11 +1877,11 @@
       <c r="D20" s="18"/>
       <c r="E20" s="21">
         <f t="shared" ref="E20:F20" si="13">E19-C20</f>
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F20" s="22">
         <f t="shared" si="13"/>
-        <v>30</v>
+        <v>25.5</v>
       </c>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
@@ -1896,11 +1913,11 @@
       <c r="D21" s="18"/>
       <c r="E21" s="21">
         <f t="shared" ref="E21:F21" si="14">E20-C21</f>
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F21" s="22">
         <f t="shared" si="14"/>
-        <v>30</v>
+        <v>25.5</v>
       </c>
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>

--- a/others/BURNDOWN-CHART.xlsx
+++ b/others/BURNDOWN-CHART.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/enric/Documents/UNI Informatica/3r - Q2/E.Software/Projecte/others/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFD7C60C-220D-6845-8389-0907E3B299F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{057CA23A-8B30-3540-BB90-831D12B339F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -58,9 +58,6 @@
     <t>PROJECT ID</t>
   </si>
   <si>
-    <t>1.0</t>
-  </si>
-  <si>
     <t>PILOT-0628</t>
   </si>
   <si>
@@ -87,6 +84,9 @@
   <si>
     <t>QUEMENGES</t>
   </si>
+  <si>
+    <t>2.0</t>
+  </si>
 </sst>
 </file>
 
@@ -95,7 +95,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -140,6 +140,12 @@
     </font>
     <font>
       <sz val="12"/>
+      <color theme="1"/>
+      <name val="Century Gothic"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Century Gothic"/>
       <family val="1"/>
@@ -490,9 +496,6 @@
     <xf numFmtId="164" fontId="3" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="3" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -546,6 +549,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1173,7 +1179,7 @@
   <sheetData>
     <row r="1" spans="1:26" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2"/>
-      <c r="B1" s="23" t="s">
+      <c r="B1" s="22" t="s">
         <v>0</v>
       </c>
       <c r="G1" s="1"/>
@@ -1198,13 +1204,13 @@
     </row>
     <row r="2" spans="1:26" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3"/>
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="26"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="25"/>
       <c r="G2" s="4" t="s">
         <v>2</v>
       </c>
@@ -1236,22 +1242,22 @@
     </row>
     <row r="3" spans="1:26" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3"/>
-      <c r="B3" s="27" t="s">
+      <c r="B3" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="27"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="27"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="8">
+        <v>46146</v>
+      </c>
+      <c r="I3" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="8">
-        <v>46096</v>
-      </c>
-      <c r="I3" s="9" t="s">
+      <c r="J3" s="9" t="s">
         <v>6</v>
-      </c>
-      <c r="J3" s="10" t="s">
-        <v>7</v>
       </c>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
@@ -1300,23 +1306,23 @@
     </row>
     <row r="5" spans="1:26" ht="69.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1"/>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="D5" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="E5" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="F5" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="G5" s="14" t="s">
         <v>12</v>
-      </c>
-      <c r="G5" s="15" t="s">
-        <v>13</v>
       </c>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
@@ -1340,19 +1346,19 @@
     </row>
     <row r="6" spans="1:26" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
-      <c r="B6" s="16">
+      <c r="B6" s="15">
         <v>0</v>
       </c>
-      <c r="C6" s="17">
+      <c r="C6" s="16">
         <v>0</v>
       </c>
-      <c r="D6" s="18">
+      <c r="D6" s="17">
         <v>0</v>
       </c>
-      <c r="E6" s="19">
+      <c r="E6" s="18">
         <v>38</v>
       </c>
-      <c r="F6" s="20">
+      <c r="F6" s="19">
         <v>38</v>
       </c>
       <c r="G6" s="1"/>
@@ -1378,20 +1384,20 @@
     </row>
     <row r="7" spans="1:26" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1"/>
-      <c r="B7" s="16">
+      <c r="B7" s="15">
         <v>1</v>
       </c>
-      <c r="C7" s="17">
+      <c r="C7" s="16">
         <v>1</v>
       </c>
-      <c r="D7" s="18">
+      <c r="D7" s="17">
         <v>1</v>
       </c>
-      <c r="E7" s="21">
+      <c r="E7" s="20">
         <f t="shared" ref="E7:F7" si="0">E6-C7</f>
         <v>37</v>
       </c>
-      <c r="F7" s="22">
+      <c r="F7" s="21">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
@@ -1418,20 +1424,20 @@
     </row>
     <row r="8" spans="1:26" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1"/>
-      <c r="B8" s="16">
+      <c r="B8" s="15">
         <v>2</v>
       </c>
-      <c r="C8" s="17">
+      <c r="C8" s="16">
         <v>2</v>
       </c>
-      <c r="D8" s="18">
+      <c r="D8" s="17">
         <v>1</v>
       </c>
-      <c r="E8" s="21">
+      <c r="E8" s="20">
         <f t="shared" ref="E8:F8" si="1">E7-C8</f>
         <v>35</v>
       </c>
-      <c r="F8" s="22">
+      <c r="F8" s="21">
         <f t="shared" si="1"/>
         <v>36</v>
       </c>
@@ -1458,20 +1464,20 @@
     </row>
     <row r="9" spans="1:26" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1"/>
-      <c r="B9" s="16">
+      <c r="B9" s="15">
         <v>3</v>
       </c>
-      <c r="C9" s="17">
+      <c r="C9" s="16">
         <v>4</v>
       </c>
-      <c r="D9" s="18">
+      <c r="D9" s="17">
         <v>4</v>
       </c>
-      <c r="E9" s="21">
+      <c r="E9" s="20">
         <f t="shared" ref="E9:F9" si="2">E8-C9</f>
         <v>31</v>
       </c>
-      <c r="F9" s="22">
+      <c r="F9" s="21">
         <f t="shared" si="2"/>
         <v>32</v>
       </c>
@@ -1498,20 +1504,20 @@
     </row>
     <row r="10" spans="1:26" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1"/>
-      <c r="B10" s="16">
+      <c r="B10" s="15">
         <v>4</v>
       </c>
-      <c r="C10" s="17">
+      <c r="C10" s="16">
         <v>2</v>
       </c>
-      <c r="D10" s="18">
+      <c r="D10" s="17">
         <v>2</v>
       </c>
-      <c r="E10" s="21">
+      <c r="E10" s="20">
         <f t="shared" ref="E10:F10" si="3">E9-C10</f>
         <v>29</v>
       </c>
-      <c r="F10" s="22">
+      <c r="F10" s="21">
         <f t="shared" si="3"/>
         <v>30</v>
       </c>
@@ -1538,20 +1544,20 @@
     </row>
     <row r="11" spans="1:26" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1"/>
-      <c r="B11" s="16">
+      <c r="B11" s="15">
         <v>5</v>
       </c>
-      <c r="C11" s="17">
+      <c r="C11" s="16">
         <v>2</v>
       </c>
-      <c r="D11" s="18">
+      <c r="D11" s="17">
         <v>2</v>
       </c>
-      <c r="E11" s="21">
+      <c r="E11" s="20">
         <f t="shared" ref="E11:F11" si="4">E10-C11</f>
         <v>27</v>
       </c>
-      <c r="F11" s="22">
+      <c r="F11" s="21">
         <f t="shared" si="4"/>
         <v>28</v>
       </c>
@@ -1578,20 +1584,20 @@
     </row>
     <row r="12" spans="1:26" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1"/>
-      <c r="B12" s="16">
+      <c r="B12" s="15">
         <v>6</v>
       </c>
-      <c r="C12" s="17">
+      <c r="C12" s="16">
         <v>3</v>
       </c>
-      <c r="D12" s="30">
+      <c r="D12" s="29">
         <v>2.5</v>
       </c>
-      <c r="E12" s="21">
+      <c r="E12" s="20">
         <f t="shared" ref="E12:F12" si="5">E11-C12</f>
         <v>24</v>
       </c>
-      <c r="F12" s="22">
+      <c r="F12" s="21">
         <f t="shared" si="5"/>
         <v>25.5</v>
       </c>
@@ -1618,16 +1624,16 @@
     </row>
     <row r="13" spans="1:26" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1"/>
-      <c r="B13" s="16">
+      <c r="B13" s="15">
         <v>7</v>
       </c>
-      <c r="C13" s="17"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="21">
+      <c r="C13" s="16"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="20">
         <f t="shared" ref="E13:F13" si="6">E12-C13</f>
         <v>24</v>
       </c>
-      <c r="F13" s="22">
+      <c r="F13" s="21">
         <f t="shared" si="6"/>
         <v>25.5</v>
       </c>
@@ -1654,16 +1660,16 @@
     </row>
     <row r="14" spans="1:26" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1"/>
-      <c r="B14" s="16">
+      <c r="B14" s="15">
         <v>8</v>
       </c>
-      <c r="C14" s="17"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="21">
+      <c r="C14" s="16"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="20">
         <f t="shared" ref="E14:F14" si="7">E13-C14</f>
         <v>24</v>
       </c>
-      <c r="F14" s="22">
+      <c r="F14" s="21">
         <f t="shared" si="7"/>
         <v>25.5</v>
       </c>
@@ -1690,16 +1696,16 @@
     </row>
     <row r="15" spans="1:26" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1"/>
-      <c r="B15" s="16">
+      <c r="B15" s="15">
         <v>9</v>
       </c>
-      <c r="C15" s="17"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="21">
+      <c r="C15" s="16"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="20">
         <f t="shared" ref="E15:F15" si="8">E14-C15</f>
         <v>24</v>
       </c>
-      <c r="F15" s="22">
+      <c r="F15" s="21">
         <f t="shared" si="8"/>
         <v>25.5</v>
       </c>
@@ -1726,16 +1732,16 @@
     </row>
     <row r="16" spans="1:26" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1"/>
-      <c r="B16" s="16">
+      <c r="B16" s="15">
         <v>10</v>
       </c>
-      <c r="C16" s="17"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="21">
+      <c r="C16" s="16"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="20">
         <f t="shared" ref="E16:F16" si="9">E15-C16</f>
         <v>24</v>
       </c>
-      <c r="F16" s="22">
+      <c r="F16" s="21">
         <f t="shared" si="9"/>
         <v>25.5</v>
       </c>
@@ -1762,16 +1768,16 @@
     </row>
     <row r="17" spans="1:26" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="1"/>
-      <c r="B17" s="16">
+      <c r="B17" s="15">
         <v>11</v>
       </c>
-      <c r="C17" s="17"/>
-      <c r="D17" s="18"/>
-      <c r="E17" s="21">
+      <c r="C17" s="16"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="20">
         <f t="shared" ref="E17:F17" si="10">E16-C17</f>
         <v>24</v>
       </c>
-      <c r="F17" s="22">
+      <c r="F17" s="21">
         <f t="shared" si="10"/>
         <v>25.5</v>
       </c>
@@ -1798,16 +1804,16 @@
     </row>
     <row r="18" spans="1:26" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="1"/>
-      <c r="B18" s="16">
+      <c r="B18" s="15">
         <v>12</v>
       </c>
-      <c r="C18" s="17"/>
-      <c r="D18" s="18"/>
-      <c r="E18" s="21">
+      <c r="C18" s="16"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="20">
         <f t="shared" ref="E18:F18" si="11">E17-C18</f>
         <v>24</v>
       </c>
-      <c r="F18" s="22">
+      <c r="F18" s="21">
         <f t="shared" si="11"/>
         <v>25.5</v>
       </c>
@@ -1834,16 +1840,16 @@
     </row>
     <row r="19" spans="1:26" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="1"/>
-      <c r="B19" s="16">
+      <c r="B19" s="15">
         <v>13</v>
       </c>
-      <c r="C19" s="17"/>
-      <c r="D19" s="18"/>
-      <c r="E19" s="21">
+      <c r="C19" s="16"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="20">
         <f t="shared" ref="E19:F19" si="12">E18-C19</f>
         <v>24</v>
       </c>
-      <c r="F19" s="22">
+      <c r="F19" s="21">
         <f t="shared" si="12"/>
         <v>25.5</v>
       </c>
@@ -1870,16 +1876,16 @@
     </row>
     <row r="20" spans="1:26" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="1"/>
-      <c r="B20" s="16">
+      <c r="B20" s="15">
         <v>14</v>
       </c>
-      <c r="C20" s="17"/>
-      <c r="D20" s="18"/>
-      <c r="E20" s="21">
+      <c r="C20" s="16"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="20">
         <f t="shared" ref="E20:F20" si="13">E19-C20</f>
         <v>24</v>
       </c>
-      <c r="F20" s="22">
+      <c r="F20" s="21">
         <f t="shared" si="13"/>
         <v>25.5</v>
       </c>
@@ -1906,16 +1912,16 @@
     </row>
     <row r="21" spans="1:26" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="1"/>
-      <c r="B21" s="16">
+      <c r="B21" s="15">
         <v>15</v>
       </c>
-      <c r="C21" s="17"/>
-      <c r="D21" s="18"/>
-      <c r="E21" s="21">
+      <c r="C21" s="16"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="20">
         <f t="shared" ref="E21:F21" si="14">E20-C21</f>
         <v>24</v>
       </c>
-      <c r="F21" s="22">
+      <c r="F21" s="21">
         <f t="shared" si="14"/>
         <v>25.5</v>
       </c>

--- a/others/BURNDOWN-CHART.xlsx
+++ b/others/BURNDOWN-CHART.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/enric/Documents/UNI Informatica/3r - Q2/E.Software/Projecte/others/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{057CA23A-8B30-3540-BB90-831D12B339F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2E53B8D-9246-844F-9385-87794C27646A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -85,7 +85,7 @@
     <t>QUEMENGES</t>
   </si>
   <si>
-    <t>2.0</t>
+    <t>3.0</t>
   </si>
 </sst>
 </file>
@@ -538,6 +538,12 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -548,12 +554,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -639,31 +639,31 @@
                   <c:v>24</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>24</c:v>
+                  <c:v>21</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>24</c:v>
+                  <c:v>17</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>24</c:v>
+                  <c:v>17</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>24</c:v>
+                  <c:v>17</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>24</c:v>
+                  <c:v>17</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>24</c:v>
+                  <c:v>17</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>24</c:v>
+                  <c:v>17</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>24</c:v>
+                  <c:v>17</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>24</c:v>
+                  <c:v>17</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -721,31 +721,31 @@
                   <c:v>25.5</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>25.5</c:v>
+                  <c:v>22</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>25.5</c:v>
+                  <c:v>18.5</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>25.5</c:v>
+                  <c:v>18.5</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>25.5</c:v>
+                  <c:v>18.5</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>25.5</c:v>
+                  <c:v>18.5</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>25.5</c:v>
+                  <c:v>18.5</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>25.5</c:v>
+                  <c:v>18.5</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>25.5</c:v>
+                  <c:v>18.5</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>25.5</c:v>
+                  <c:v>18.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1204,13 +1204,13 @@
     </row>
     <row r="2" spans="1:26" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3"/>
-      <c r="B2" s="23" t="s">
+      <c r="B2" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="25"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="27"/>
       <c r="G2" s="4" t="s">
         <v>2</v>
       </c>
@@ -1242,18 +1242,18 @@
     </row>
     <row r="3" spans="1:26" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3"/>
-      <c r="B3" s="26" t="s">
+      <c r="B3" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="27"/>
-      <c r="D3" s="27"/>
-      <c r="E3" s="27"/>
-      <c r="F3" s="28"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="29"/>
+      <c r="F3" s="30"/>
       <c r="G3" s="7"/>
       <c r="H3" s="8">
         <v>46146</v>
       </c>
-      <c r="I3" s="30" t="s">
+      <c r="I3" s="24" t="s">
         <v>14</v>
       </c>
       <c r="J3" s="9" t="s">
@@ -1590,7 +1590,7 @@
       <c r="C12" s="16">
         <v>3</v>
       </c>
-      <c r="D12" s="29">
+      <c r="D12" s="23">
         <v>2.5</v>
       </c>
       <c r="E12" s="20">
@@ -1627,15 +1627,19 @@
       <c r="B13" s="15">
         <v>7</v>
       </c>
-      <c r="C13" s="16"/>
-      <c r="D13" s="17"/>
+      <c r="C13" s="16">
+        <v>3</v>
+      </c>
+      <c r="D13" s="17">
+        <v>3.5</v>
+      </c>
       <c r="E13" s="20">
         <f t="shared" ref="E13:F13" si="6">E12-C13</f>
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F13" s="21">
         <f t="shared" si="6"/>
-        <v>25.5</v>
+        <v>22</v>
       </c>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
@@ -1663,15 +1667,19 @@
       <c r="B14" s="15">
         <v>8</v>
       </c>
-      <c r="C14" s="16"/>
-      <c r="D14" s="17"/>
+      <c r="C14" s="16">
+        <v>4</v>
+      </c>
+      <c r="D14" s="17">
+        <v>3.5</v>
+      </c>
       <c r="E14" s="20">
         <f t="shared" ref="E14:F14" si="7">E13-C14</f>
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F14" s="21">
         <f t="shared" si="7"/>
-        <v>25.5</v>
+        <v>18.5</v>
       </c>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
@@ -1703,11 +1711,11 @@
       <c r="D15" s="17"/>
       <c r="E15" s="20">
         <f t="shared" ref="E15:F15" si="8">E14-C15</f>
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F15" s="21">
         <f t="shared" si="8"/>
-        <v>25.5</v>
+        <v>18.5</v>
       </c>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
@@ -1739,11 +1747,11 @@
       <c r="D16" s="17"/>
       <c r="E16" s="20">
         <f t="shared" ref="E16:F16" si="9">E15-C16</f>
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F16" s="21">
         <f t="shared" si="9"/>
-        <v>25.5</v>
+        <v>18.5</v>
       </c>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
@@ -1775,11 +1783,11 @@
       <c r="D17" s="17"/>
       <c r="E17" s="20">
         <f t="shared" ref="E17:F17" si="10">E16-C17</f>
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F17" s="21">
         <f t="shared" si="10"/>
-        <v>25.5</v>
+        <v>18.5</v>
       </c>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
@@ -1811,11 +1819,11 @@
       <c r="D18" s="17"/>
       <c r="E18" s="20">
         <f t="shared" ref="E18:F18" si="11">E17-C18</f>
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F18" s="21">
         <f t="shared" si="11"/>
-        <v>25.5</v>
+        <v>18.5</v>
       </c>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
@@ -1847,11 +1855,11 @@
       <c r="D19" s="17"/>
       <c r="E19" s="20">
         <f t="shared" ref="E19:F19" si="12">E18-C19</f>
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F19" s="21">
         <f t="shared" si="12"/>
-        <v>25.5</v>
+        <v>18.5</v>
       </c>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
@@ -1883,11 +1891,11 @@
       <c r="D20" s="17"/>
       <c r="E20" s="20">
         <f t="shared" ref="E20:F20" si="13">E19-C20</f>
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F20" s="21">
         <f t="shared" si="13"/>
-        <v>25.5</v>
+        <v>18.5</v>
       </c>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
@@ -1919,11 +1927,11 @@
       <c r="D21" s="17"/>
       <c r="E21" s="20">
         <f t="shared" ref="E21:F21" si="14">E20-C21</f>
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F21" s="21">
         <f t="shared" si="14"/>
-        <v>25.5</v>
+        <v>18.5</v>
       </c>
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>

--- a/others/BURNDOWN-CHART.xlsx
+++ b/others/BURNDOWN-CHART.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/enric/Documents/UNI Informatica/3r - Q2/E.Software/Projecte/others/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2E53B8D-9246-844F-9385-87794C27646A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F73D10F9-0A49-4F47-BB8E-C24A81E8A1D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -85,7 +85,7 @@
     <t>QUEMENGES</t>
   </si>
   <si>
-    <t>3.0</t>
+    <t>4.0</t>
   </si>
 </sst>
 </file>
@@ -645,25 +645,25 @@
                   <c:v>17</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>17</c:v>
+                  <c:v>14</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>17</c:v>
+                  <c:v>11</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>17</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>17</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>17</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>17</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>17</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -727,25 +727,25 @@
                   <c:v>18.5</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>18.5</c:v>
+                  <c:v>15</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>18.5</c:v>
+                  <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>18.5</c:v>
+                  <c:v>8.5</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>18.5</c:v>
+                  <c:v>6.5</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>18.5</c:v>
+                  <c:v>6.5</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>18.5</c:v>
+                  <c:v>6.5</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>18.5</c:v>
+                  <c:v>6.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1707,15 +1707,19 @@
       <c r="B15" s="15">
         <v>9</v>
       </c>
-      <c r="C15" s="16"/>
-      <c r="D15" s="17"/>
+      <c r="C15" s="16">
+        <v>3</v>
+      </c>
+      <c r="D15" s="17">
+        <v>3.5</v>
+      </c>
       <c r="E15" s="20">
         <f t="shared" ref="E15:F15" si="8">E14-C15</f>
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F15" s="21">
         <f t="shared" si="8"/>
-        <v>18.5</v>
+        <v>15</v>
       </c>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
@@ -1743,15 +1747,19 @@
       <c r="B16" s="15">
         <v>10</v>
       </c>
-      <c r="C16" s="16"/>
-      <c r="D16" s="17"/>
+      <c r="C16" s="16">
+        <v>3</v>
+      </c>
+      <c r="D16" s="17">
+        <v>3</v>
+      </c>
       <c r="E16" s="20">
         <f t="shared" ref="E16:F16" si="9">E15-C16</f>
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F16" s="21">
         <f t="shared" si="9"/>
-        <v>18.5</v>
+        <v>12</v>
       </c>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
@@ -1779,15 +1787,19 @@
       <c r="B17" s="15">
         <v>11</v>
       </c>
-      <c r="C17" s="16"/>
-      <c r="D17" s="17"/>
+      <c r="C17" s="16">
+        <v>4</v>
+      </c>
+      <c r="D17" s="17">
+        <v>3.5</v>
+      </c>
       <c r="E17" s="20">
         <f t="shared" ref="E17:F17" si="10">E16-C17</f>
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="F17" s="21">
         <f t="shared" si="10"/>
-        <v>18.5</v>
+        <v>8.5</v>
       </c>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
@@ -1815,15 +1827,19 @@
       <c r="B18" s="15">
         <v>12</v>
       </c>
-      <c r="C18" s="16"/>
-      <c r="D18" s="17"/>
+      <c r="C18" s="16">
+        <v>2</v>
+      </c>
+      <c r="D18" s="17">
+        <v>2</v>
+      </c>
       <c r="E18" s="20">
         <f t="shared" ref="E18:F18" si="11">E17-C18</f>
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="F18" s="21">
         <f t="shared" si="11"/>
-        <v>18.5</v>
+        <v>6.5</v>
       </c>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
@@ -1855,11 +1871,11 @@
       <c r="D19" s="17"/>
       <c r="E19" s="20">
         <f t="shared" ref="E19:F19" si="12">E18-C19</f>
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="F19" s="21">
         <f t="shared" si="12"/>
-        <v>18.5</v>
+        <v>6.5</v>
       </c>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
@@ -1891,11 +1907,11 @@
       <c r="D20" s="17"/>
       <c r="E20" s="20">
         <f t="shared" ref="E20:F20" si="13">E19-C20</f>
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="F20" s="21">
         <f t="shared" si="13"/>
-        <v>18.5</v>
+        <v>6.5</v>
       </c>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
@@ -1927,11 +1943,11 @@
       <c r="D21" s="17"/>
       <c r="E21" s="20">
         <f t="shared" ref="E21:F21" si="14">E20-C21</f>
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="F21" s="21">
         <f t="shared" si="14"/>
-        <v>18.5</v>
+        <v>6.5</v>
       </c>
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
